--- a/Test Scenarios.xlsx
+++ b/Test Scenarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Opencart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97A8607-80AA-488D-8B55-2285A9E74FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC264E3B-84AE-457C-9BDA-C438250A0420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,7 +747,9 @@
       <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="7">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -762,7 +764,9 @@
       <c r="D3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="10">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -777,7 +781,9 @@
       <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
@@ -792,7 +798,9 @@
       <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="10">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -807,7 +815,9 @@
       <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -822,7 +832,9 @@
       <c r="D7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10">
+        <v>24</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
@@ -837,7 +849,9 @@
       <c r="D8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="7">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
@@ -852,7 +866,9 @@
       <c r="D9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
@@ -867,7 +883,9 @@
       <c r="D10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
@@ -882,7 +900,9 @@
       <c r="D11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="10"/>
+      <c r="E11" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
@@ -897,7 +917,9 @@
       <c r="D12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="7">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
@@ -912,7 +934,9 @@
       <c r="D13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="10">
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
@@ -927,7 +951,9 @@
       <c r="D14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="7">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
@@ -942,7 +968,9 @@
       <c r="D15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="10">
+        <v>13</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
@@ -957,7 +985,9 @@
       <c r="D16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -972,7 +1002,9 @@
       <c r="D17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="10"/>
+      <c r="E17" s="10">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
@@ -987,7 +1019,9 @@
       <c r="D18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="7">
+        <v>8</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -1002,7 +1036,9 @@
       <c r="D19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="10">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -1017,7 +1053,9 @@
       <c r="D20" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
@@ -1032,7 +1070,9 @@
       <c r="D21" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="10">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
@@ -1047,7 +1087,9 @@
       <c r="D22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="7">
+        <v>9</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -1062,7 +1104,9 @@
       <c r="D23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7">
+        <v>14</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
@@ -1077,7 +1121,9 @@
       <c r="D24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="10"/>
+      <c r="E24" s="10">
+        <v>13</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
@@ -1092,7 +1138,9 @@
       <c r="D25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="10"/>
+      <c r="E25" s="10">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -1107,7 +1155,9 @@
       <c r="D26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
